--- a/datosSesionesOutput.xlsx
+++ b/datosSesionesOutput.xlsx
@@ -2006,13 +2006,13 @@
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-14507.376</v>
+        <v>2688.697</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>

--- a/datosSesionesOutput.xlsx
+++ b/datosSesionesOutput.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -578,6 +588,12 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="n">
+        <v>78.5714285714285</v>
+      </c>
+      <c r="U2" t="n">
+        <v>21.4285714285714</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -637,6 +653,12 @@
       <c r="S3" t="n">
         <v>2</v>
       </c>
+      <c r="T3" t="n">
+        <v>88.235294117647</v>
+      </c>
+      <c r="U3" t="n">
+        <v>11.7647058823529</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -696,6 +718,12 @@
       <c r="S4" t="n">
         <v>1</v>
       </c>
+      <c r="T4" t="n">
+        <v>84.6153846153846</v>
+      </c>
+      <c r="U4" t="n">
+        <v>15.3846153846153</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -754,6 +782,12 @@
       </c>
       <c r="S5" t="n">
         <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>84.21052631578939</v>
+      </c>
+      <c r="U5" t="n">
+        <v>15.7894736842105</v>
       </c>
     </row>
     <row r="6">
@@ -814,6 +848,12 @@
       <c r="S6" t="n">
         <v>1</v>
       </c>
+      <c r="T6" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -873,6 +913,12 @@
       <c r="S7" t="n">
         <v>1</v>
       </c>
+      <c r="T7" t="n">
+        <v>95</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -932,6 +978,16 @@
       <c r="S8" t="n">
         <v>2</v>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -991,6 +1047,12 @@
       <c r="S9" t="n">
         <v>2</v>
       </c>
+      <c r="T9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1050,6 +1112,12 @@
       <c r="S10" t="n">
         <v>4</v>
       </c>
+      <c r="T10" t="n">
+        <v>95.2380952380952</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.76190476190475</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1109,6 +1177,12 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
+      <c r="T11" t="n">
+        <v>92.8571428571428</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7.14285714285713</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1168,6 +1242,12 @@
       <c r="S12" t="n">
         <v>1</v>
       </c>
+      <c r="T12" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1227,6 +1307,12 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
+      <c r="T13" t="n">
+        <v>76.4705882352941</v>
+      </c>
+      <c r="U13" t="n">
+        <v>23.5294117647058</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1286,6 +1372,12 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
+      <c r="T14" t="n">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="U14" t="n">
+        <v>13.3333333333333</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1345,6 +1437,12 @@
       <c r="S15" t="n">
         <v>1</v>
       </c>
+      <c r="T15" t="n">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>16.6666666666666</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1404,6 +1502,12 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
+      <c r="T16" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>18.75</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1463,6 +1567,12 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
+      <c r="T17" t="n">
+        <v>92.5925925925926</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7.4074074074074</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1522,6 +1632,16 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1581,6 +1701,12 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
+      <c r="T19" t="n">
+        <v>90.3225806451613</v>
+      </c>
+      <c r="U19" t="n">
+        <v>9.677419354838699</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1640,6 +1766,12 @@
       <c r="S20" t="n">
         <v>1</v>
       </c>
+      <c r="T20" t="n">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9.09090909090909</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1699,6 +1831,12 @@
       <c r="S21" t="n">
         <v>0</v>
       </c>
+      <c r="T21" t="n">
+        <v>94.73684210526309</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5.26315789473683</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1758,6 +1896,12 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
+      <c r="T22" t="n">
+        <v>88.6363636363636</v>
+      </c>
+      <c r="U22" t="n">
+        <v>11.3636363636363</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1817,6 +1961,12 @@
       <c r="S23" t="n">
         <v>0</v>
       </c>
+      <c r="T23" t="n">
+        <v>78.5714285714285</v>
+      </c>
+      <c r="U23" t="n">
+        <v>21.4285714285714</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1876,6 +2026,12 @@
       <c r="S24" t="n">
         <v>4</v>
       </c>
+      <c r="T24" t="n">
+        <v>50</v>
+      </c>
+      <c r="U24" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1935,6 +2091,12 @@
       <c r="S25" t="n">
         <v>0</v>
       </c>
+      <c r="T25" t="n">
+        <v>76.7441860465116</v>
+      </c>
+      <c r="U25" t="n">
+        <v>23.2558139534883</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1994,6 +2156,12 @@
       <c r="S26" t="n">
         <v>1</v>
       </c>
+      <c r="T26" t="n">
+        <v>95</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2053,6 +2221,12 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
+      <c r="T27" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2112,6 +2286,12 @@
       <c r="S28" t="n">
         <v>2</v>
       </c>
+      <c r="T28" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2171,6 +2351,12 @@
       <c r="S29" t="n">
         <v>2</v>
       </c>
+      <c r="T29" t="n">
+        <v>75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2230,6 +2416,12 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
+      <c r="T30" t="n">
+        <v>60</v>
+      </c>
+      <c r="U30" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2289,6 +2481,12 @@
       <c r="S31" t="n">
         <v>3</v>
       </c>
+      <c r="T31" t="n">
+        <v>75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2348,6 +2546,12 @@
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2407,6 +2611,12 @@
       <c r="S33" t="n">
         <v>0</v>
       </c>
+      <c r="T33" t="n">
+        <v>78.9473684210526</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21.0526315789473</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2466,6 +2676,12 @@
       <c r="S34" t="n">
         <v>2</v>
       </c>
+      <c r="T34" t="n">
+        <v>76.78571428571421</v>
+      </c>
+      <c r="U34" t="n">
+        <v>23.2142857142857</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2525,6 +2741,12 @@
       <c r="S35" t="n">
         <v>3</v>
       </c>
+      <c r="T35" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="U35" t="n">
+        <v>7.69230769230769</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2584,6 +2806,12 @@
       <c r="S36" t="n">
         <v>3</v>
       </c>
+      <c r="T36" t="n">
+        <v>83.7837837837837</v>
+      </c>
+      <c r="U36" t="n">
+        <v>16.2162162162162</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2643,6 +2871,12 @@
       <c r="S37" t="n">
         <v>1</v>
       </c>
+      <c r="T37" t="n">
+        <v>90.2439024390244</v>
+      </c>
+      <c r="U37" t="n">
+        <v>9.756097560975601</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2702,6 +2936,12 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
+      <c r="T38" t="n">
+        <v>90.4761904761904</v>
+      </c>
+      <c r="U38" t="n">
+        <v>9.52380952380951</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2761,6 +3001,16 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2820,6 +3070,16 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2879,6 +3139,16 @@
       <c r="S41" t="n">
         <v>4</v>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2938,6 +3208,12 @@
       <c r="S42" t="n">
         <v>2</v>
       </c>
+      <c r="T42" t="n">
+        <v>83.8709677419354</v>
+      </c>
+      <c r="U42" t="n">
+        <v>16.1290322580645</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2997,6 +3273,12 @@
       <c r="S43" t="n">
         <v>1</v>
       </c>
+      <c r="T43" t="n">
+        <v>80.7692307692307</v>
+      </c>
+      <c r="U43" t="n">
+        <v>19.2307692307692</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3056,6 +3338,12 @@
       <c r="S44" t="n">
         <v>2</v>
       </c>
+      <c r="T44" t="n">
+        <v>96.4285714285714</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3.57142857142856</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3115,6 +3403,16 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3174,6 +3472,16 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3233,6 +3541,12 @@
       <c r="S47" t="n">
         <v>1</v>
       </c>
+      <c r="T47" t="n">
+        <v>80.95238095238091</v>
+      </c>
+      <c r="U47" t="n">
+        <v>19.047619047619</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -3292,6 +3606,16 @@
       <c r="S48" t="n">
         <v>2</v>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3351,6 +3675,12 @@
       <c r="S49" t="n">
         <v>0</v>
       </c>
+      <c r="T49" t="n">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="U49" t="n">
+        <v>11.1111111111111</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3410,6 +3740,12 @@
       <c r="S50" t="n">
         <v>2</v>
       </c>
+      <c r="T50" t="n">
+        <v>78.7878787878787</v>
+      </c>
+      <c r="U50" t="n">
+        <v>21.2121212121212</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3469,6 +3805,16 @@
       <c r="S51" t="n">
         <v>1</v>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3528,6 +3874,12 @@
       <c r="S52" t="n">
         <v>5</v>
       </c>
+      <c r="T52" t="n">
+        <v>57.1428571428571</v>
+      </c>
+      <c r="U52" t="n">
+        <v>42.8571428571428</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3587,6 +3939,12 @@
       <c r="S53" t="n">
         <v>6</v>
       </c>
+      <c r="T53" t="n">
+        <v>90</v>
+      </c>
+      <c r="U53" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3646,6 +4004,12 @@
       <c r="S54" t="n">
         <v>2</v>
       </c>
+      <c r="T54" t="n">
+        <v>75</v>
+      </c>
+      <c r="U54" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3705,6 +4069,12 @@
       <c r="S55" t="n">
         <v>0</v>
       </c>
+      <c r="T55" t="n">
+        <v>100</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3764,6 +4134,12 @@
       <c r="S56" t="n">
         <v>7</v>
       </c>
+      <c r="T56" t="n">
+        <v>50</v>
+      </c>
+      <c r="U56" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -3823,6 +4199,12 @@
       <c r="S57" t="n">
         <v>2</v>
       </c>
+      <c r="T57" t="n">
+        <v>94.11764705882349</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5.88235294117646</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3882,6 +4264,12 @@
       <c r="S58" t="n">
         <v>0</v>
       </c>
+      <c r="T58" t="n">
+        <v>83.6065573770491</v>
+      </c>
+      <c r="U58" t="n">
+        <v>16.3934426229508</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -3941,6 +4329,12 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
+      <c r="T59" t="n">
+        <v>57.1428571428571</v>
+      </c>
+      <c r="U59" t="n">
+        <v>42.8571428571428</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4000,6 +4394,12 @@
       <c r="S60" t="n">
         <v>0</v>
       </c>
+      <c r="T60" t="n">
+        <v>91.6666666666666</v>
+      </c>
+      <c r="U60" t="n">
+        <v>8.33333333333332</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4059,6 +4459,12 @@
       <c r="S61" t="n">
         <v>1</v>
       </c>
+      <c r="T61" t="n">
+        <v>90.625</v>
+      </c>
+      <c r="U61" t="n">
+        <v>9.375</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4118,6 +4524,12 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
+      <c r="T62" t="n">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="U62" t="n">
+        <v>13.3333333333333</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4177,6 +4589,12 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
+      <c r="T63" t="n">
+        <v>89.28571428571421</v>
+      </c>
+      <c r="U63" t="n">
+        <v>10.7142857142857</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4236,6 +4654,12 @@
       <c r="S64" t="n">
         <v>3</v>
       </c>
+      <c r="T64" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="U64" t="n">
+        <v>43.75</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4295,6 +4719,12 @@
       <c r="S65" t="n">
         <v>0</v>
       </c>
+      <c r="T65" t="n">
+        <v>100</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4354,6 +4784,12 @@
       <c r="S66" t="n">
         <v>0</v>
       </c>
+      <c r="T66" t="n">
+        <v>75</v>
+      </c>
+      <c r="U66" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4413,6 +4849,12 @@
       <c r="S67" t="n">
         <v>1</v>
       </c>
+      <c r="T67" t="n">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="U67" t="n">
+        <v>7.69230769230769</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4472,6 +4914,12 @@
       <c r="S68" t="n">
         <v>0</v>
       </c>
+      <c r="T68" t="n">
+        <v>96.29629629629621</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3.7037037037037</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4531,6 +4979,12 @@
       <c r="S69" t="n">
         <v>1</v>
       </c>
+      <c r="T69" t="n">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="U69" t="n">
+        <v>33.3333333333333</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4590,6 +5044,16 @@
       <c r="S70" t="n">
         <v>0</v>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4649,6 +5113,12 @@
       <c r="S71" t="n">
         <v>0</v>
       </c>
+      <c r="T71" t="n">
+        <v>75.8620689655172</v>
+      </c>
+      <c r="U71" t="n">
+        <v>24.1379310344827</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4708,6 +5178,16 @@
       <c r="S72" t="n">
         <v>0</v>
       </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>0 planificado</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -4767,6 +5247,12 @@
       <c r="S73" t="n">
         <v>0</v>
       </c>
+      <c r="T73" t="n">
+        <v>71.4285714285714</v>
+      </c>
+      <c r="U73" t="n">
+        <v>28.5714285714285</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -4826,6 +5312,12 @@
       <c r="S74" t="n">
         <v>2</v>
       </c>
+      <c r="T74" t="n">
+        <v>76</v>
+      </c>
+      <c r="U74" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -4885,6 +5377,12 @@
       <c r="S75" t="n">
         <v>0</v>
       </c>
+      <c r="T75" t="n">
+        <v>91.3043478260869</v>
+      </c>
+      <c r="U75" t="n">
+        <v>8.695652173913039</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -4943,6 +5441,12 @@
       </c>
       <c r="S76" t="n">
         <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>77.1428571428571</v>
+      </c>
+      <c r="U76" t="n">
+        <v>22.8571428571428</v>
       </c>
     </row>
   </sheetData>
